--- a/data/trans_orig/IQ2601_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ2601_R2-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81045</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73422</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>87116</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>69,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>68658</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>62282</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>74964</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>61816</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>74591</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>76,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>69,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>81045</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>73640</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>87327</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>76,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139433</t>
+          <t>140894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158519</t>
+          <t>158932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,0%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24903</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18832</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32526</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21603</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15297</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27979</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15670</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28445</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,93%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24903</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18621</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32308</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37689</t>
+          <t>37276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56775</t>
+          <t>55314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>189172</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>178272</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>200582</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>74,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>70,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>79,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>187021</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>175769</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>197317</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>175579</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>199110</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>73,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>69,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>78,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>189172</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>176986</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>199726</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>74,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>358746</t>
+          <t>359376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390500</t>
+          <t>389670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,93%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64584</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53174</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75484</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>65736</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>55440</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76988</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>53647</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>77178</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>26,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>64584</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76770</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>25,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116014</t>
+          <t>116844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147768</t>
+          <t>147138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>94633</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85075</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>102872</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>86968</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78282</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95684</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>77801</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>94967</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>68,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>94633</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>84837</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>103441</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168863</t>
+          <t>169277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193808</t>
+          <t>192758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46882</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>38643</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56440</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>40580</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31864</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49266</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>32581</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>49747</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>31,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>46882</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>38074</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>56678</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75255</t>
+          <t>76305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100200</t>
+          <t>99786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>97623</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>86044</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>109015</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>47,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>41,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>108391</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97223</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>118269</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>95829</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>118073</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>55,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>50,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>97623</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>87079</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>108827</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190575</t>
+          <t>189830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222175</t>
+          <t>220196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>108426</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>97034</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>120005</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>52,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>58,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>85706</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75828</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96874</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>76024</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>98268</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>44,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>108426</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>97222</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>118970</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>52,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177971</t>
+          <t>179950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209571</t>
+          <t>210316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>462474</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>440089</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>481463</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>62,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>451037</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>432164</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>469291</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>433101</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>470992</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>67,86%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>462474</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>439742</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>480392</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>887289</t>
+          <t>885396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>940472</t>
+          <t>942134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>244794</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>225805</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>267179</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>213626</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>195372</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>232499</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>193671</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>231562</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>244794</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>226876</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>267526</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>431458</t>
+          <t>429796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>484641</t>
+          <t>486534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2675,67 +2675,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>65191</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54916</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73250</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>60213</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51334</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>68872</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>51962</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>69377</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>65191</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>56098</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>74283</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>54,98%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112032</t>
+          <t>112036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137212</t>
+          <t>138065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53384</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45325</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63659</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45,02%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>64261</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55602</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73140</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>55097</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72512</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>51,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>53384</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>44292</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62477</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>45,02%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105837</t>
+          <t>104984</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131017</t>
+          <t>131013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>124474</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>124474</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>124474</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>150141</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>137249</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>164959</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>51,02%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>140922</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>127660</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>153269</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>129491</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>154747</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>59,83%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>54,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>150141</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>134967</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>164249</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>55,82%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>271228</t>
+          <t>273346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>307939</t>
+          <t>309034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,25%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>118850</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>104032</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>131742</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>38,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>94616</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>82269</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>107878</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80791</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>106047</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>40,17%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>118850</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>104742</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>134024</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>44,18%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196590</t>
+          <t>195495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233301</t>
+          <t>231183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>235538</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>235538</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>235538</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82646</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>71940</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>92519</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>75590</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65131</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>86170</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>65819</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>86303</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>48,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>82646</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>72420</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>92969</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142893</t>
+          <t>142409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173942</t>
+          <t>173030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75925</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66052</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86631</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80844</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70264</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>91303</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70131</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>90615</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>51,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>58,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75925</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65602</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86151</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>47,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141063</t>
+          <t>141975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172112</t>
+          <t>172596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58236</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48099</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68408</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>84384</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>72898</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>95199</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>73027</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>94530</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>49,25%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>42,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>58236</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>49184</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>68927</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127700</t>
+          <t>126965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156295</t>
+          <t>157140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>121719</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>111547</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>131856</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>86953</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>76138</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>98439</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>76807</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>98310</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>50,75%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>57,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>121719</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>111028</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>130771</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>67,64%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>194997</t>
+          <t>194152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223592</t>
+          <t>224327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>356214</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>332768</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>378199</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>361108</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>337344</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>381526</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>340065</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>382882</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>52,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>356214</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>331716</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>378087</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>687891</t>
+          <t>687930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>749600</t>
+          <t>751363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>369878</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>347893</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>393324</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>47,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>326675</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>306257</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>350439</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>304901</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>347718</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>47,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>369878</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>348005</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>394376</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664275</t>
+          <t>662512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>725984</t>
+          <t>725945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>990</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>687783</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>687783</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>687783</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69959</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61164</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>77520</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>62770</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>53420</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71036</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>53548</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71262</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>51,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>69959</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>60796</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>78364</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>59,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120445</t>
+          <t>120375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144534</t>
+          <t>145863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46692</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39131</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55487</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58053</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49787</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67403</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49561</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67275</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>48,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>46692</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38287</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55855</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92940</t>
+          <t>91611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117029</t>
+          <t>117099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>167598</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>155566</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>179551</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>64,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>69,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>137578</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>126439</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>148192</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>126637</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>148881</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>65,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>60,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>167598</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>154800</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>178274</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>64,95%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>289302</t>
+          <t>288541</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321619</t>
+          <t>320977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90463</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78510</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>102495</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>39,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>72939</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>62325</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>84078</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>61636</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>83880</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>34,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>39,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>90463</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>79787</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>35,05%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146959</t>
+          <t>147601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179276</t>
+          <t>180037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>126230</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>116305</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>136623</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>129205</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>118576</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>139901</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>118566</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>138659</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>68,4%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>62,77%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>126230</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>115350</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>136351</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,94%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236506</t>
+          <t>238305</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268952</t>
+          <t>269415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62342</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51949</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>72267</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>59694</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48998</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>70323</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>50240</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>70333</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>31,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>37,23%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>62342</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52221</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73222</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,06%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>173</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108519</t>
+          <t>108056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140965</t>
+          <t>139166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,74 +5646,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>110561</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>99260</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>121572</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>57,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>69,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>114713</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>103593</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>103082</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>125072</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>66,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>59,48%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>72,17%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>110561</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>98622</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>120381</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>63,52%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>56,66%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>69,17%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>313</t>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209898</t>
+          <t>209045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239390</t>
+          <t>239242</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>63487</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52476</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>74788</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>58588</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>48229</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>69708</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>70219</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>33,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>27,83%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>63487</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>53667</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>75426</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>36,48%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107958</t>
+          <t>108106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137450</t>
+          <t>138303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>474348</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>451187</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>497019</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>444266</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>424179</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>463217</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>422565</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>463696</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,06%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>474348</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>453926</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>495865</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>887063</t>
+          <t>890646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>948036</t>
+          <t>946107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>262984</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>240313</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>286145</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>374</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>249274</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>230323</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>269361</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>229844</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>270975</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,94%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>262984</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>241467</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>283406</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>482835</t>
+          <t>484764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>543808</t>
+          <t>540225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9466</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7488</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10721</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9746</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6782</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11972</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>73,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3678</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3590</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6554</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>26,92%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13336</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13336</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13336</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26760</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21473</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30855</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>54,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>25534</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21448</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29360</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>74,36%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55965</t>
+          <t>48727</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49055</t>
+          <t>42086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>54124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12719</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8624</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18006</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>45,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8806</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4980</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12892</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16944</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>27991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39873</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33262</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45036</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>74,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>62,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>29091</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23378</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33693</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>72,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42300</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36090</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47256</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>71391</t>
+          <t>67123</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62986</t>
+          <t>58007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78886</t>
+          <t>73731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13420</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8257</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20031</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10916</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6314</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16629</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>27,29%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19827</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>24533</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17038</t>
+          <t>18018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>33742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54779</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46030</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61387</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>82,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>34612</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28546</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40624</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>63,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>52,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55923</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47871</t>
+          <t>29352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63194</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>90535</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79947</t>
+          <t>81374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100876</t>
+          <t>100520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,41%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19647</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13039</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28396</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>19759</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13747</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25825</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>47,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>40604</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30274</t>
+          <t>31040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51203</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54371</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54371</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>54371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131150</t>
+          <t>131560</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131150</t>
+          <t>131560</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131150</t>
+          <t>131560</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119578</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140854</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>98984</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>89370</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107503</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128483</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152196</t>
+          <t>103047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>239232</t>
+          <t>225183</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223897</t>
+          <t>211054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252531</t>
+          <t>238878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>47487</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>58787</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>32,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>43071</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34552</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>52685</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>30,32%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63287</t>
+          <t>53535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>94592</t>
+          <t>91739</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81293</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109927</t>
+          <t>105868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
